--- a/data/trans_camb/IP16B08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B08-Clase-trans_camb.xlsx
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,24</t>
+          <t>0,0; 43,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,56</t>
+          <t>0,0; 47,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,99</t>
+          <t>0,0; 42,33</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,34</t>
+          <t>0,0; 78,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,24</t>
+          <t>0,0; 90,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,21</t>
+          <t>0,0; 73,68</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 0,0</t>
+          <t>-40,32; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 0,0</t>
+          <t>-30,07; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 0,0</t>
+          <t>-40,32; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 0,0</t>
+          <t>-30,07; 0,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 7,59</t>
+          <t>-22,61; 7,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,12</t>
+          <t>0,0; 18,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 4,26</t>
+          <t>-15,19; 4,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,51</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 8,2</t>
+          <t>-23,2; 8,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,64</t>
+          <t>0,0; 22,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 4,45</t>
+          <t>-15,27; 4,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,74</t>
+          <t>0,0; 12,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B08-Clase-trans_camb.xlsx
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,95</t>
+          <t>0,0; 54,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,49</t>
+          <t>0,0; 48,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,33</t>
+          <t>0,0; 47,93</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,42</t>
+          <t>0,0; 121,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 90,49</t>
+          <t>0,0; 95,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,68</t>
+          <t>0,0; 92,06</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 0,0</t>
+          <t>-42,17; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 0,0</t>
+          <t>-29,41; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 0,0</t>
+          <t>-42,17; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 0,0</t>
+          <t>-29,41; 0,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-22,61; 7,6</t>
+          <t>-22,52; 7,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,49</t>
+          <t>0,0; 20,19</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 4,19</t>
+          <t>-12,59; 4,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,8</t>
+          <t>0,0; 8,63</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 8,21</t>
+          <t>-22,78; 8,1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,68</t>
+          <t>0,0; 25,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 4,37</t>
+          <t>-12,78; 4,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,11</t>
+          <t>0,0; 9,44</t>
         </is>
       </c>
     </row>
